--- a/cadastro_rede.xlsx
+++ b/cadastro_rede.xlsx
@@ -16,13 +16,14 @@
     <sheet name="teste" sheetId="7" r:id="rId7"/>
     <sheet name="ti" sheetId="8" r:id="rId8"/>
     <sheet name="depart_test" sheetId="9" r:id="rId9"/>
+    <sheet name="depart-teste" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="141">
   <si>
     <t>CADASTRO DE REDE</t>
   </si>
@@ -409,6 +410,42 @@
   </si>
   <si>
     <t>dfgdfgdfgd</t>
+  </si>
+  <si>
+    <t>resrte</t>
+  </si>
+  <si>
+    <t>asdas</t>
+  </si>
+  <si>
+    <t>testado@gmail.com</t>
+  </si>
+  <si>
+    <t>depart-teste</t>
+  </si>
+  <si>
+    <t>teste-subsecretaria</t>
+  </si>
+  <si>
+    <t>testtt</t>
+  </si>
+  <si>
+    <t>tes.tt</t>
+  </si>
+  <si>
+    <t>teste@asdasd</t>
+  </si>
+  <si>
+    <t>jkljç</t>
+  </si>
+  <si>
+    <t>çjkçjkç</t>
+  </si>
+  <si>
+    <t>jkljkljkl</t>
+  </si>
+  <si>
+    <t>ljkljkl</t>
   </si>
 </sst>
 </file>
@@ -520,6 +557,49 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2344897</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>850229</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="niteroi.png"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="142875" y="95250"/>
+          <a:ext cx="2202022" cy="754979"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -1339,6 +1419,184 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="40.7109375" customWidth="1"/>
+    <col min="2" max="2" width="35.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="45.7109375" customWidth="1"/>
+    <col min="5" max="5" width="25.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="70" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="4">
+        <v>2</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A13:E13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E15"/>
@@ -2731,10 +2989,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>120</v>
+        <v>12</v>
+      </c>
+      <c r="B10" s="4">
+        <v>2</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -2742,10 +3000,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="4">
-        <v>2</v>
+        <v>119</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
